--- a/artfynd/A 37647-2026 artfynd.xlsx
+++ b/artfynd/A 37647-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136971706</v>
       </c>
       <c r="B2" t="n">
-        <v>83455</v>
+        <v>83459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136971601</v>
       </c>
       <c r="B3" t="n">
-        <v>96688</v>
+        <v>96694</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>136971727</v>
       </c>
       <c r="B4" t="n">
-        <v>96688</v>
+        <v>96694</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>136971363</v>
       </c>
       <c r="B5" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136971437</v>
       </c>
       <c r="B6" t="n">
-        <v>83446</v>
+        <v>83450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2026 artfynd.xlsx
+++ b/artfynd/A 37647-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136971706</v>
       </c>
       <c r="B2" t="n">
-        <v>83459</v>
+        <v>83461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136971601</v>
       </c>
       <c r="B3" t="n">
-        <v>96694</v>
+        <v>96696</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>136971727</v>
       </c>
       <c r="B4" t="n">
-        <v>96694</v>
+        <v>96696</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>136971363</v>
       </c>
       <c r="B5" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136971437</v>
       </c>
       <c r="B6" t="n">
-        <v>83450</v>
+        <v>83452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2026 artfynd.xlsx
+++ b/artfynd/A 37647-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136971706</v>
       </c>
       <c r="B2" t="n">
-        <v>83461</v>
+        <v>83462</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136971601</v>
       </c>
       <c r="B3" t="n">
-        <v>96696</v>
+        <v>96697</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>136971727</v>
       </c>
       <c r="B4" t="n">
-        <v>96696</v>
+        <v>96697</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>136971363</v>
       </c>
       <c r="B5" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136971437</v>
       </c>
       <c r="B6" t="n">
-        <v>83452</v>
+        <v>83453</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2026 artfynd.xlsx
+++ b/artfynd/A 37647-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>136971601</v>
       </c>
       <c r="B3" t="n">
-        <v>96697</v>
+        <v>96703</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>136971727</v>
       </c>
       <c r="B4" t="n">
-        <v>96697</v>
+        <v>96703</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2026 artfynd.xlsx
+++ b/artfynd/A 37647-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136971706</v>
       </c>
       <c r="B2" t="n">
-        <v>83462</v>
+        <v>83466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136971601</v>
       </c>
       <c r="B3" t="n">
-        <v>96703</v>
+        <v>96707</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>136971727</v>
       </c>
       <c r="B4" t="n">
-        <v>96703</v>
+        <v>96707</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>136971363</v>
       </c>
       <c r="B5" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136971437</v>
       </c>
       <c r="B6" t="n">
-        <v>83453</v>
+        <v>83457</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2026 artfynd.xlsx
+++ b/artfynd/A 37647-2026 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>136971601</v>
       </c>
       <c r="B3" t="n">
-        <v>96707</v>
+        <v>96709</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>136971727</v>
       </c>
       <c r="B4" t="n">
-        <v>96707</v>
+        <v>96709</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2026 artfynd.xlsx
+++ b/artfynd/A 37647-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136971706</v>
       </c>
       <c r="B2" t="n">
-        <v>83466</v>
+        <v>83468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136971601</v>
       </c>
       <c r="B3" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>136971727</v>
       </c>
       <c r="B4" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>136971363</v>
       </c>
       <c r="B5" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136971437</v>
       </c>
       <c r="B6" t="n">
-        <v>83457</v>
+        <v>83459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2026 artfynd.xlsx
+++ b/artfynd/A 37647-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136971706</v>
       </c>
       <c r="B2" t="n">
-        <v>83468</v>
+        <v>83481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136971601</v>
       </c>
       <c r="B3" t="n">
-        <v>96711</v>
+        <v>96724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>136971727</v>
       </c>
       <c r="B4" t="n">
-        <v>96711</v>
+        <v>96724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>136971363</v>
       </c>
       <c r="B5" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136971437</v>
       </c>
       <c r="B6" t="n">
-        <v>83459</v>
+        <v>83472</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>136971279</v>
       </c>
       <c r="B7" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>136971319</v>
       </c>
       <c r="B8" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2026 artfynd.xlsx
+++ b/artfynd/A 37647-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136971706</v>
       </c>
       <c r="B2" t="n">
-        <v>83481</v>
+        <v>83483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136971601</v>
       </c>
       <c r="B3" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>136971727</v>
       </c>
       <c r="B4" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>136971363</v>
       </c>
       <c r="B5" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136971437</v>
       </c>
       <c r="B6" t="n">
-        <v>83472</v>
+        <v>83474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>136971279</v>
       </c>
       <c r="B7" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>136971319</v>
       </c>
       <c r="B8" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>136971787</v>
       </c>
       <c r="B9" t="n">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>136971852</v>
       </c>
       <c r="B10" t="n">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2026 artfynd.xlsx
+++ b/artfynd/A 37647-2026 artfynd.xlsx
@@ -710,11 +710,7 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -841,11 +837,7 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -980,11 +972,7 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -1263,11 +1251,7 @@
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1406,11 +1390,7 @@
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1539,11 +1519,7 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1667,17 +1643,9 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1811,17 +1779,9 @@
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>

--- a/artfynd/A 37647-2026 artfynd.xlsx
+++ b/artfynd/A 37647-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136971706</v>
       </c>
       <c r="B2" t="n">
-        <v>83483</v>
+        <v>83486</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136971601</v>
       </c>
       <c r="B3" t="n">
-        <v>96726</v>
+        <v>96729</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136971727</v>
       </c>
       <c r="B4" t="n">
-        <v>96726</v>
+        <v>96729</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>136971437</v>
       </c>
       <c r="B6" t="n">
-        <v>83474</v>
+        <v>83477</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2026 artfynd.xlsx
+++ b/artfynd/A 37647-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136971706</v>
       </c>
       <c r="B2" t="n">
-        <v>83486</v>
+        <v>83496</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136971601</v>
       </c>
       <c r="B3" t="n">
-        <v>96729</v>
+        <v>96739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136971727</v>
       </c>
       <c r="B4" t="n">
-        <v>96729</v>
+        <v>96739</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>136971363</v>
       </c>
       <c r="B5" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>136971437</v>
       </c>
       <c r="B6" t="n">
-        <v>83477</v>
+        <v>83487</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136971279</v>
       </c>
       <c r="B7" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>136971319</v>
       </c>
       <c r="B8" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>136971787</v>
       </c>
       <c r="B9" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>136971852</v>
       </c>
       <c r="B10" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2026 artfynd.xlsx
+++ b/artfynd/A 37647-2026 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>136971601</v>
       </c>
       <c r="B3" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136971727</v>
       </c>
       <c r="B4" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2026 artfynd.xlsx
+++ b/artfynd/A 37647-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136971706</v>
       </c>
       <c r="B2" t="n">
-        <v>83496</v>
+        <v>83499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136971601</v>
       </c>
       <c r="B3" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136971727</v>
       </c>
       <c r="B4" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>136971363</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>136971437</v>
       </c>
       <c r="B6" t="n">
-        <v>83487</v>
+        <v>83490</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136971279</v>
       </c>
       <c r="B7" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>136971319</v>
       </c>
       <c r="B8" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2026 artfynd.xlsx
+++ b/artfynd/A 37647-2026 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>136971601</v>
       </c>
       <c r="B3" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136971727</v>
       </c>
       <c r="B4" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2026 artfynd.xlsx
+++ b/artfynd/A 37647-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136971706</v>
       </c>
       <c r="B2" t="n">
-        <v>83499</v>
+        <v>83504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136971601</v>
       </c>
       <c r="B3" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136971727</v>
       </c>
       <c r="B4" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>136971363</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>136971437</v>
       </c>
       <c r="B6" t="n">
-        <v>83490</v>
+        <v>83495</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136971279</v>
       </c>
       <c r="B7" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>136971319</v>
       </c>
       <c r="B8" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2026 artfynd.xlsx
+++ b/artfynd/A 37647-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136971706</v>
       </c>
       <c r="B2" t="n">
-        <v>83504</v>
+        <v>83515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136971601</v>
       </c>
       <c r="B3" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136971727</v>
       </c>
       <c r="B4" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>136971363</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>136971437</v>
       </c>
       <c r="B6" t="n">
-        <v>83495</v>
+        <v>83506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2026 artfynd.xlsx
+++ b/artfynd/A 37647-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136971706</v>
       </c>
       <c r="B2" t="n">
-        <v>83515</v>
+        <v>83516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136971601</v>
       </c>
       <c r="B3" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136971727</v>
       </c>
       <c r="B4" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>136971363</v>
       </c>
       <c r="B5" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>136971437</v>
       </c>
       <c r="B6" t="n">
-        <v>83506</v>
+        <v>83507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2026 artfynd.xlsx
+++ b/artfynd/A 37647-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136971706</v>
       </c>
       <c r="B2" t="n">
-        <v>83516</v>
+        <v>83518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136971601</v>
       </c>
       <c r="B3" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136971727</v>
       </c>
       <c r="B4" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>136971363</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>136971437</v>
       </c>
       <c r="B6" t="n">
-        <v>83507</v>
+        <v>83509</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2026 artfynd.xlsx
+++ b/artfynd/A 37647-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136971706</v>
       </c>
       <c r="B2" t="n">
-        <v>83518</v>
+        <v>83519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136971601</v>
       </c>
       <c r="B3" t="n">
-        <v>96769</v>
+        <v>96770</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136971727</v>
       </c>
       <c r="B4" t="n">
-        <v>96769</v>
+        <v>96770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>136971363</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>136971437</v>
       </c>
       <c r="B6" t="n">
-        <v>83509</v>
+        <v>83510</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2026 artfynd.xlsx
+++ b/artfynd/A 37647-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136971706</v>
       </c>
       <c r="B2" t="n">
-        <v>83519</v>
+        <v>83522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136971601</v>
       </c>
       <c r="B3" t="n">
-        <v>96770</v>
+        <v>96773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136971727</v>
       </c>
       <c r="B4" t="n">
-        <v>96770</v>
+        <v>96773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>136971363</v>
       </c>
       <c r="B5" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>136971437</v>
       </c>
       <c r="B6" t="n">
-        <v>83510</v>
+        <v>83513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136971279</v>
       </c>
       <c r="B7" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>136971319</v>
       </c>
       <c r="B8" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
